--- a/couple-budget-template.xlsx
+++ b/couple-budget-template.xlsx
@@ -4,13 +4,14 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="基金清單" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="預算" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="交易" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="月度報表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="快速記帳" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="_-&quot;$&quot;* #,##0.00_-;-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,6 +54,13 @@
     <font>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00C00000"/>
     </font>
   </fonts>
   <fills count="7">
@@ -114,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -134,6 +142,16 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -11647,4 +11665,266 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>快速記帳（巨集輔助）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>填好輸入區後按對應按鈕（需先把檔案另存為 .xlsm 並匯入 CoupleBudget.bas，詳見下方步驟）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>新增交易</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>新增預算</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>日常</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>基金</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>日常</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>月份 (YYYY-MM)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>類型</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>金額</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr"/>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>記錄人</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>金額</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr"/>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>備註</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>記錄人</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>備註</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr"/>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>→ 在此處附近插入按鈕並指派巨集 AddBudget</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>→ 在此處附近插入按鈕並指派巨集 AddTransaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>巨集設定步驟（一次性，約 2 分鐘）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1. 把這個 .xlsx 「另存新檔」 → 檔案類型選「Excel 啟用巨集的活頁簿 (.xlsm)」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2. 按 Alt + F11 開啟 VBA 編輯器。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3. 上方選單 File → Import File... → 選擇 scripts/macros/CoupleBudget.bas。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4. 關閉 VBA 編輯器，回到 Excel。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5. 確認看到「開發人員」索引標籤；沒看到時：檔案 → 選項 → 自訂功能區 → 勾「開發人員」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>6. 開發人員 → 插入 → 表單控制項「按鈕」→ 在交易輸入區下方拖出一個按鈕，跳出視窗時選 AddTransaction。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>7. 同樣步驟在預算輸入區下方插入按鈕，指派 AddBudget。可右鍵按鈕 → 編輯文字 改成「新增交易」/「新增預算」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>8. 儲存檔案。之後填好黃色輸入區、按按鈕即可。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A12:B12"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>=基金清單!$A$5:$A$9</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"收入,支出"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>=基金清單!$A$5:$A$9</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>